--- a/DataTables/Datas/skill.xlsx
+++ b/DataTables/Datas/skill.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="4" min="1" max="3"/>
@@ -571,6 +571,11 @@
           <t>cooldown</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>hitdelay</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -641,6 +646,11 @@
       <c r="N2" s="6" t="inlineStr">
         <is>
           <t>int</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>float</t>
         </is>
       </c>
     </row>
@@ -734,6 +744,14 @@
       <c r="N3" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>出伤延迟秒数
+0=打击时刻立即结算
+&gt;0=命中后延迟该秒数再扣血
+(spine关键帧作为后续扩展)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -776,6 +794,9 @@
       <c r="N4" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -816,6 +837,9 @@
       </c>
       <c r="M5" s="6" t="n"/>
       <c r="N5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -860,6 +884,9 @@
       <c r="N6" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="5">
       <c r="A7" s="9" t="n"/>
@@ -902,6 +929,9 @@
       <c r="N7" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="5">
       <c r="A8" s="9" t="n"/>
@@ -944,6 +974,9 @@
       <c r="N8" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="27" customFormat="1" customHeight="1" s="5">
       <c r="A9" s="9" t="n"/>
@@ -990,6 +1023,9 @@
         </is>
       </c>
       <c r="N9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0</v>
       </c>
     </row>
